--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484131_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484131_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1138</v>
+        <v>3.9034</v>
       </c>
       <c r="E2" t="n">
-        <v>3.2351</v>
+        <v>2.2772</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8787</v>
+        <v>1.6262</v>
       </c>
       <c r="G2" t="n">
         <v>2.244</v>
@@ -610,13 +610,13 @@
         <v>1.1903</v>
       </c>
       <c r="S2" t="n">
-        <v>1.6795</v>
+        <v>0.469</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3548</v>
+        <v>0.3968</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3247</v>
+        <v>0.0722</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>N. BAQUES GARCIA</t>
+          <t>V. CASTELLON MARTIN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.1386</v>
+        <v>3.7321</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4391</v>
+        <v>3.5276</v>
       </c>
       <c r="F3" t="n">
-        <v>3.5777</v>
+        <v>0.2046</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2121</v>
+        <v>0.6811</v>
       </c>
       <c r="H3" t="n">
-        <v>0.716</v>
+        <v>0.5541</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.504</v>
+        <v>0.127</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.0974</v>
+        <v>1.7943</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2228</v>
+        <v>0.469</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.3202</v>
+        <v>1.3253</v>
       </c>
       <c r="M3" t="n">
-        <v>1.3095</v>
+        <v>-1.1132</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4932</v>
+        <v>0.0851</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8162</v>
+        <v>-1.1983</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.1903</v>
+        <v>0.9919</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.7855</v>
+        <v>0.9919</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7752</v>
+        <v>-0.08790000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2924</v>
+        <v>0.2608</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4828</v>
+        <v>-0.3486</v>
       </c>
       <c r="V3" t="n">
-        <v>2.3417</v>
+        <v>2.1469</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3417</v>
+        <v>1.4724</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.029</v>
+        <v>2.6551</v>
       </c>
       <c r="E4" t="n">
-        <v>1.55</v>
+        <v>1.2042</v>
       </c>
       <c r="F4" t="n">
-        <v>1.479</v>
+        <v>1.4509</v>
       </c>
       <c r="G4" t="n">
         <v>2.5768</v>
@@ -766,13 +766,13 @@
         <v>0.9919</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0436</v>
+        <v>-0.3302</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0567</v>
+        <v>-0.289</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0131</v>
+        <v>-0.0412</v>
       </c>
       <c r="V4" t="n">
         <v>0.4085</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>V. CASTELLON MARTIN</t>
+          <t>A. ALEXANDRE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.9414</v>
+        <v>1.7565</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0174</v>
+        <v>1.9633</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.076</v>
+        <v>-0.2068</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6811</v>
+        <v>2.2063</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5541</v>
+        <v>2.6662</v>
       </c>
       <c r="I5" t="n">
-        <v>0.127</v>
+        <v>-0.4599</v>
       </c>
       <c r="J5" t="n">
-        <v>1.7943</v>
+        <v>2.7114</v>
       </c>
       <c r="K5" t="n">
-        <v>0.469</v>
+        <v>2.5106</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3253</v>
+        <v>0.2008</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1132</v>
+        <v>-0.5051</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0851</v>
+        <v>0.1556</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.1983</v>
+        <v>-0.6607</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9919</v>
+        <v>0.5952</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9919</v>
+        <v>1.5871</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8786</v>
+        <v>-0.513</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2494</v>
+        <v>0.2438</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6292</v>
+        <v>-0.7568</v>
       </c>
       <c r="V5" t="n">
-        <v>2.1469</v>
+        <v>-0.532</v>
       </c>
       <c r="W5" t="n">
-        <v>1.4724</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6745</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X. ISERN MAZA</t>
+          <t>N. BAQUES GARCIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9096</v>
+        <v>1.7318</v>
       </c>
       <c r="E6" t="n">
-        <v>1.1675</v>
+        <v>-1.397</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7421</v>
+        <v>3.1288</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1846</v>
+        <v>0.2121</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.716</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1089</v>
+        <v>-0.504</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8193</v>
+        <v>-1.0974</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0562</v>
+        <v>0.2228</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7631</v>
+        <v>-1.3202</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6347</v>
+        <v>1.3095</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0195</v>
+        <v>0.4932</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.6542</v>
+        <v>0.8162</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5952</v>
+        <v>-1.1903</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9919</v>
+        <v>-2.9758</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5871</v>
+        <v>1.7855</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5266</v>
+        <v>0.3684</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7369</v>
+        <v>0.3345</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2104</v>
+        <v>0.0339</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6032</v>
+        <v>2.3417</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6032</v>
+        <v>2.3417</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. ALEXANDRE</t>
+          <t>X. ISERN MAZA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.476</v>
+        <v>1.5856</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9633</v>
+        <v>0.7594</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4873</v>
+        <v>0.8262</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2063</v>
+        <v>0.1846</v>
       </c>
       <c r="H7" t="n">
-        <v>2.6662</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.4599</v>
+        <v>0.1089</v>
       </c>
       <c r="J7" t="n">
-        <v>2.7114</v>
+        <v>0.8193</v>
       </c>
       <c r="K7" t="n">
-        <v>2.5106</v>
+        <v>0.0562</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2008</v>
+        <v>0.7631</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5051</v>
+        <v>-0.6347</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1556</v>
+        <v>0.0195</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6607</v>
+        <v>-0.6542</v>
       </c>
       <c r="P7" t="n">
         <v>0.5952</v>
@@ -1000,28 +1000,28 @@
         <v>1.5871</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7935</v>
+        <v>0.2026</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2438</v>
+        <v>0.3288</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0373</v>
+        <v>-0.1262</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.532</v>
+        <v>0.6032</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.6032</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. FONT RODRIGUEZ</t>
+          <t>M. ESTEBAN CALVO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1963</v>
+        <v>0.5023</v>
       </c>
       <c r="E8" t="n">
-        <v>1.3121</v>
+        <v>-0.36</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5084</v>
+        <v>0.8623</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4095</v>
+        <v>0.9207</v>
       </c>
       <c r="H8" t="n">
-        <v>1.315</v>
+        <v>-1.0537</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0945</v>
+        <v>1.9744</v>
       </c>
       <c r="J8" t="n">
-        <v>1.8457</v>
+        <v>1.4144</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3561</v>
+        <v>-1.0781</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4896</v>
+        <v>2.4926</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4363</v>
+        <v>-0.4937</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0412</v>
+        <v>0.0244</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.3951</v>
+        <v>-0.5182</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3968</v>
+        <v>0.1984</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3887</v>
+        <v>2.1822</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1928</v>
+        <v>-0.8828</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7481</v>
+        <v>-0.0566</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5554</v>
+        <v>-0.8262</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.8097</v>
+        <v>0.266</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2065</v>
+        <v>0.266</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.0162</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. RIBAS BLANCO</t>
+          <t>D. FONT RODRIGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5306999999999999</v>
+        <v>-0.1084</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1007</v>
+        <v>1.6806</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6314</v>
+        <v>-1.7889</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2283</v>
+        <v>1.4095</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6299</v>
+        <v>1.315</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4016</v>
+        <v>0.0945</v>
       </c>
       <c r="J9" t="n">
-        <v>0.625</v>
+        <v>1.8457</v>
       </c>
       <c r="K9" t="n">
-        <v>0.625</v>
+        <v>1.3561</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.4896</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3967</v>
+        <v>-0.4363</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0049</v>
+        <v>-0.0412</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4016</v>
+        <v>-0.3951</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>0.3968</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.3887</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4217</v>
+        <v>-0.1049</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.187</v>
+        <v>-0.3797</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2347</v>
+        <v>0.2748</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3373</v>
+        <v>-1.8097</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3373</v>
+        <v>1.2065</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-3.0162</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. ESTEBAN CALVO</t>
+          <t>X. GUIA HORMIGON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.6787</v>
+        <v>-0.3388</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1763</v>
+        <v>-1.5419</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4976</v>
+        <v>1.2031</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9207</v>
+        <v>-0.0794</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0537</v>
+        <v>0.1861</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9744</v>
+        <v>-0.2656</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4144</v>
+        <v>-0.312</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.0781</v>
+        <v>0.3682</v>
       </c>
       <c r="L10" t="n">
-        <v>2.4926</v>
+        <v>-0.6802</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4937</v>
+        <v>0.2325</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0244</v>
+        <v>-0.1821</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5182</v>
+        <v>0.4146</v>
       </c>
       <c r="P10" t="n">
         <v>0.1984</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1822</v>
+        <v>1.1903</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.0638</v>
+        <v>-0.4577</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8728</v>
+        <v>-0.238</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1909</v>
+        <v>-0.2197</v>
       </c>
       <c r="V10" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X. GUIA HORMIGON</t>
+          <t>R. RIBAS BLANCO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,64 +1267,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9393</v>
+        <v>-0.4746</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.1144</v>
+        <v>0.1007</v>
       </c>
       <c r="F11" t="n">
-        <v>1.1751</v>
+        <v>-0.5753</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.0794</v>
+        <v>0.2283</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1861</v>
+        <v>0.6299</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2656</v>
+        <v>-0.4016</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.312</v>
+        <v>0.625</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3682</v>
+        <v>0.625</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6802</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2325</v>
+        <v>-0.3967</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.1821</v>
+        <v>0.0049</v>
       </c>
       <c r="O11" t="n">
-        <v>0.4146</v>
+        <v>-0.4016</v>
       </c>
       <c r="P11" t="n">
-        <v>0.1984</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1903</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0583</v>
+        <v>-0.3656</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.8105</v>
+        <v>-0.187</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2478</v>
+        <v>-0.1786</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.3373</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.3373</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.4541</v>
+        <v>-0.9542</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4179</v>
+        <v>-0.8057</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.0362</v>
+        <v>-0.1484</v>
       </c>
       <c r="G12" t="n">
         <v>-0.1336</v>
@@ -1390,13 +1390,13 @@
         <v>1.9838</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1519</v>
+        <v>0.6518</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0679</v>
+        <v>0.5442</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2198</v>
+        <v>0.1076</v>
       </c>
       <c r="V12" t="n">
         <v>-1.4724</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.9313</v>
+        <v>-2.8012</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.1451</v>
+        <v>-2.0431</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.7861</v>
+        <v>-0.7581</v>
       </c>
       <c r="G13" t="n">
         <v>-2.6892</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.242</v>
+        <v>-0.1119</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1247</v>
+        <v>-0.0227</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1173</v>
+        <v>-0.0893</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>10.878</v>
+        <v>11.1896</v>
       </c>
       <c r="E14" t="n">
-        <v>5.053300000000002</v>
+        <v>5.3653</v>
       </c>
       <c r="F14" t="n">
-        <v>5.824800000000002</v>
+        <v>5.8246</v>
       </c>
       <c r="G14" t="n">
         <v>7.761200000000002</v>
@@ -1516,7 +1516,7 @@
         <v>8.441399999999998</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.6802000000000002</v>
+        <v>-0.6802000000000005</v>
       </c>
       <c r="J14" t="n">
         <v>10.7797</v>
@@ -1525,13 +1525,13 @@
         <v>8.901700000000002</v>
       </c>
       <c r="L14" t="n">
-        <v>1.8781</v>
+        <v>1.878099999999999</v>
       </c>
       <c r="M14" t="n">
         <v>-3.0186</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4605000000000001</v>
+        <v>-0.4605</v>
       </c>
       <c r="O14" t="n">
         <v>-2.5583</v>
@@ -1546,19 +1546,19 @@
         <v>14.8788</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4739</v>
+        <v>-1.1622</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6241999999999998</v>
+        <v>0.9358999999999998</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.098</v>
+        <v>-2.0981</v>
       </c>
       <c r="V14" t="n">
         <v>1.6149</v>
       </c>
       <c r="W14" t="n">
-        <v>5.5525</v>
+        <v>5.552499999999999</v>
       </c>
       <c r="X14" t="n">
         <v>-3.9376</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.9888</v>
+        <v>5.2566</v>
       </c>
       <c r="E15" t="n">
-        <v>6.0465</v>
+        <v>6.4546</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0577</v>
+        <v>-1.198</v>
       </c>
       <c r="G15" t="n">
         <v>2.6459</v>
@@ -1624,13 +1624,13 @@
         <v>1.5871</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4506</v>
+        <v>-0.1828</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2436</v>
+        <v>0.1645</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.207</v>
+        <v>-0.3473</v>
       </c>
       <c r="V15" t="n">
         <v>1.2065</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6291</v>
+        <v>1.3816</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6893</v>
+        <v>1.3015</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0602</v>
+        <v>0.0801</v>
       </c>
       <c r="G16" t="n">
         <v>0.7911</v>
@@ -1702,13 +1702,13 @@
         <v>0.5952</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.0231</v>
+        <v>-0.2706</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8105</v>
+        <v>-0.1983</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2126</v>
+        <v>-0.0723</v>
       </c>
       <c r="V16" t="n">
         <v>0.266</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6287</v>
+        <v>0.7511</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4486</v>
+        <v>-0.5506</v>
       </c>
       <c r="F17" t="n">
-        <v>1.0773</v>
+        <v>1.3017</v>
       </c>
       <c r="G17" t="n">
         <v>0.8129999999999999</v>
@@ -1780,13 +1780,13 @@
         <v>1.7855</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2801</v>
+        <v>0.4025</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6122</v>
+        <v>0.5102</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3322</v>
+        <v>-0.1077</v>
       </c>
       <c r="V17" t="n">
         <v>-0.266</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3436</v>
+        <v>0.5961</v>
       </c>
       <c r="E18" t="n">
         <v>2.6301</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.2865</v>
+        <v>-2.034</v>
       </c>
       <c r="G18" t="n">
         <v>-2.4815</v>
@@ -1858,13 +1858,13 @@
         <v>1.7855</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3814</v>
+        <v>-0.1289</v>
       </c>
       <c r="T18" t="n">
         <v>0.1872</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5686</v>
+        <v>-0.3161</v>
       </c>
       <c r="V18" t="n">
         <v>2.4129</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.7257</v>
+        <v>-1.292</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0359</v>
+        <v>0.5256999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7616</v>
+        <v>-1.8177</v>
       </c>
       <c r="G19" t="n">
         <v>-0.7681</v>
@@ -1936,13 +1936,13 @@
         <v>0.9919</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3084</v>
+        <v>-0.2579</v>
       </c>
       <c r="T19" t="n">
-        <v>0.6746</v>
+        <v>0.1644</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3662</v>
+        <v>-0.4223</v>
       </c>
       <c r="V19" t="n">
         <v>-0.266</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.2776</v>
+        <v>-2.2496</v>
       </c>
       <c r="E20" t="n">
         <v>-2.875</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.6254</v>
       </c>
       <c r="G20" t="n">
         <v>-1.9907</v>
@@ -2014,13 +2014,13 @@
         <v>0.7935</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1774</v>
+        <v>0.2055</v>
       </c>
       <c r="T20" t="n">
         <v>0.0567</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1207</v>
+        <v>0.1488</v>
       </c>
       <c r="V20" t="n">
         <v>-0.266</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6339</v>
+        <v>-3.014</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.6184</v>
+        <v>-4.8022</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9846</v>
+        <v>1.7882</v>
       </c>
       <c r="G21" t="n">
         <v>-2.5883</v>
@@ -2092,13 +2092,13 @@
         <v>0.7935</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0221</v>
+        <v>0.6419</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9238</v>
+        <v>-0.1076</v>
       </c>
       <c r="U21" t="n">
-        <v>0.9459</v>
+        <v>0.7495000000000001</v>
       </c>
       <c r="V21" t="n">
         <v>-0.8692</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.765</v>
+        <v>-3.8824</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3725</v>
+        <v>0.3417</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.3925</v>
+        <v>-4.2241</v>
       </c>
       <c r="G22" t="n">
         <v>-1.8946</v>
@@ -2170,13 +2170,13 @@
         <v>1.5871</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.3898</v>
+        <v>-0.5073</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5498</v>
+        <v>0.1644</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8401</v>
+        <v>-0.6717</v>
       </c>
       <c r="V22" t="n">
         <v>-2.0757</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.0661</v>
+        <v>-8.4254</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.9119</v>
+        <v>-8.8505</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8459</v>
+        <v>0.425</v>
       </c>
       <c r="G23" t="n">
         <v>-2.2879</v>
@@ -2248,13 +2248,13 @@
         <v>1.9838</v>
       </c>
       <c r="S23" t="n">
-        <v>3.9309</v>
+        <v>1.5715</v>
       </c>
       <c r="T23" t="n">
-        <v>3.095</v>
+        <v>1.1564</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8359</v>
+        <v>0.4151</v>
       </c>
       <c r="V23" t="n">
         <v>-1.7575</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.8781</v>
+        <v>-10.878</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.824599999999999</v>
+        <v>-5.8247</v>
       </c>
       <c r="F24" t="n">
-        <v>-5.0534</v>
+        <v>-5.053400000000001</v>
       </c>
       <c r="G24" t="n">
         <v>-7.761099999999999</v>
@@ -2326,13 +2326,13 @@
         <v>11.9031</v>
       </c>
       <c r="S24" t="n">
-        <v>1.474</v>
+        <v>1.4739</v>
       </c>
       <c r="T24" t="n">
-        <v>2.098</v>
+        <v>2.0979</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.6242</v>
+        <v>-0.6239999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-1.615</v>
